--- a/produits.xlsx
+++ b/produits.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\__dev_projects\ez_facture_excel\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\__dev_projects\ezfacture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0E5135-5ED5-479F-A024-D78BAABEE3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD578C5-9F5E-4F8D-BE8F-1E35A033DD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{94078687-D3EE-445D-BBC6-74AE353569D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>Référence produit</t>
   </si>
@@ -68,18 +68,12 @@
     <t>P0001</t>
   </si>
   <si>
-    <t>Sandwich jambon beurre</t>
-  </si>
-  <si>
     <t>Bien - 5,5%</t>
   </si>
   <si>
     <t>P0002</t>
   </si>
   <si>
-    <t>Bière Heineken</t>
-  </si>
-  <si>
     <t>Bien - 10%</t>
   </si>
   <si>
@@ -117,6 +111,24 @@
   </si>
   <si>
     <t>S</t>
+  </si>
+  <si>
+    <t>VTC Giant reconditionné</t>
+  </si>
+  <si>
+    <t>Porte gourde</t>
+  </si>
+  <si>
+    <t>Aide catégories de TVA Ezfacture</t>
+  </si>
+  <si>
+    <t>B : Biens</t>
+  </si>
+  <si>
+    <t>S : services</t>
+  </si>
+  <si>
+    <t>K : Livraison intracommunautaire exonérée</t>
   </si>
 </sst>
 </file>
@@ -816,7 +828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B153B7B-D5E1-4A57-B6E3-7CEFB060E308}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -828,7 +840,7 @@
     <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -853,113 +865,125 @@
       <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
+      <c r="J1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="9">
+        <v>490</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>9</v>
-      </c>
-      <c r="C2" s="9">
-        <v>4</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>10</v>
       </c>
       <c r="E2" s="10">
         <v>5.5E-2</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="12"/>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="9">
+        <v>12</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="9">
-        <v>3</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>13</v>
       </c>
       <c r="E3" s="10">
         <v>0.1</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G3" s="11"/>
       <c r="H3" s="12"/>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C4" s="9">
         <v>9</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E4" s="10">
         <v>0.2</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="12"/>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="9">
         <v>15</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E5" s="10">
         <v>0</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="12"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C6" s="9">
         <v>50</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" s="10">
         <v>0.2</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="12"/>

--- a/produits.xlsx
+++ b/produits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\__dev_projects\ezfacture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD578C5-9F5E-4F8D-BE8F-1E35A033DD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C44A53E-92A1-4E0B-95A2-602AF0CCDFEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{94078687-D3EE-445D-BBC6-74AE353569D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>Référence produit</t>
   </si>
@@ -119,23 +119,26 @@
     <t>Porte gourde</t>
   </si>
   <si>
-    <t>Aide catégories de TVA Ezfacture</t>
-  </si>
-  <si>
     <t>B : Biens</t>
   </si>
   <si>
-    <t>S : services</t>
-  </si>
-  <si>
     <t>K : Livraison intracommunautaire exonérée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aide </t>
+  </si>
+  <si>
+    <t>Pour la colonne Cat, choisir parmi une de ces catégories (spécifique Ezfacture) :</t>
+  </si>
+  <si>
+    <t>S : Services</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,13 +161,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -211,7 +228,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -254,6 +271,8 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -838,6 +857,7 @@
     <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="75.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -865,8 +885,8 @@
       <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
-        <v>26</v>
+      <c r="J1" s="14" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -890,8 +910,8 @@
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="12"/>
-      <c r="J2" t="s">
-        <v>27</v>
+      <c r="J2" s="13" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -916,7 +936,7 @@
       <c r="G3" s="11"/>
       <c r="H3" s="12"/>
       <c r="J3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -941,7 +961,7 @@
       <c r="G4" s="11"/>
       <c r="H4" s="12"/>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -965,6 +985,9 @@
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="12"/>
+      <c r="J5" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -989,14 +1012,10 @@
       <c r="H6" s="12"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D6" xr:uid="{ECE62AA0-7513-454D-BE8A-4ED65857A84A}">
-      <formula1>liste_cat_taxes</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>